--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (14)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (16)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202CFE53-5229-4457-943A-6AC57235662F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61B7EC2-105F-4BA5-8C6C-DEABDEF01EE9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>备件价格</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>OrderNo</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>IB数量</t>
+  </si>
+  <si>
+    <t>探头描述</t>
   </si>
 </sst>
 </file>
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -541,25 +541,25 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -580,56 +580,56 @@
         <v>13</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2328E975-6B95-406D-A1DC-1FE2591DFBCB}">
       <formula1>"DI、PCB,US、Biomed,LCS,US探头"</formula1>
     </dataValidation>
@@ -661,14 +661,17 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
       <formula1>"N/A,普通,特殊,高值"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{11549471-4591-4EDB-ABC9-AB8AD11D3728}">
-      <formula1>"代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576" xr:uid="{E541982E-D725-4FDA-9EEA-792C8D21CCD5}">
       <formula1>"N/A,新入保,已入保"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{565EFFCF-906C-4E8B-B682-B8B385A4F816}">
       <formula1>"East,North,South,West"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{B09B0FC2-5F93-4797-9BA6-BC3CAD1644F0}">
+      <formula1>"Depot FE,N/A,TSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{60F15405-71E4-4B57-8AC8-C724A2E36699}">
+      <formula1>"DI,PCB,Biomed,CCS,CCS-A,CCS-B"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -690,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -698,7 +701,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (16)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61B7EC2-105F-4BA5-8C6C-DEABDEF01EE9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E05C81E-02DF-48E5-BF00-F8937D54ED66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,11 +667,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{565EFFCF-906C-4E8B-B682-B8B385A4F816}">
       <formula1>"East,North,South,West"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{B09B0FC2-5F93-4797-9BA6-BC3CAD1644F0}">
-      <formula1>"Depot FE,N/A,TSE"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{60F15405-71E4-4B57-8AC8-C724A2E36699}">
       <formula1>"DI,PCB,Biomed,CCS,CCS-A,CCS-B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
+      <formula1>"Depot FE,N/A,TSE,代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E05C81E-02DF-48E5-BF00-F8937D54ED66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041F4376-309C-412C-9B3E-BBCCB0B6A054}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>入保情况</t>
   </si>
   <si>
-    <t>Srowner</t>
-  </si>
-  <si>
     <t>删除</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>探头描述</t>
+  </si>
+  <si>
+    <t>SR Owner</t>
   </si>
 </sst>
 </file>
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -541,25 +541,25 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -580,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>14</v>
@@ -607,25 +607,25 @@
         <v>21</v>
       </c>
       <c r="AE1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -701,7 +701,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (13)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041F4376-309C-412C-9B3E-BBCCB0B6A054}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD6E08B-8E47-4DF3-9D37-02C564635279}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>系统ID</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>SR Owner</t>
+  </si>
+  <si>
+    <t>任意申请限额</t>
+  </si>
+  <si>
+    <t>普通限额</t>
+  </si>
+  <si>
+    <t>特殊限额</t>
+  </si>
+  <si>
+    <t>高值限额</t>
   </si>
 </sst>
 </file>
@@ -483,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E5EE65-1D54-4A5B-BDC5-DBB4F002F6AB}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5546875" style="2" customWidth="1"/>
@@ -505,17 +517,17 @@
     <col min="21" max="21" width="18.88671875" style="5" customWidth="1"/>
     <col min="22" max="23" width="17.33203125" style="2" customWidth="1"/>
     <col min="24" max="24" width="17.88671875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="25.88671875" style="3" customWidth="1"/>
-    <col min="26" max="27" width="19.6640625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="17.88671875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="21.44140625" style="2" customWidth="1"/>
-    <col min="30" max="33" width="22.109375" style="2" customWidth="1"/>
-    <col min="34" max="36" width="21.6640625" style="2" customWidth="1"/>
-    <col min="37" max="37" width="24.5546875" style="2" customWidth="1"/>
-    <col min="38" max="16384" width="8.88671875" style="2"/>
+    <col min="25" max="29" width="25.88671875" style="3" customWidth="1"/>
+    <col min="30" max="31" width="19.6640625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="17.88671875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="21.44140625" style="2" customWidth="1"/>
+    <col min="34" max="37" width="22.109375" style="2" customWidth="1"/>
+    <col min="38" max="40" width="21.6640625" style="2" customWidth="1"/>
+    <col min="41" max="41" width="24.5546875" style="2" customWidth="1"/>
+    <col min="42" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,39 +604,51 @@
         <v>16</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -633,7 +657,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2328E975-6B95-406D-A1DC-1FE2591DFBCB}">
       <formula1>"DI、PCB,US、Biomed,LCS,US探头"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK1048576 AF2:AF1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2:AO1048576 AJ2:AJ1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H1048576 N2:N1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
@@ -648,30 +672,30 @@
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
+      <formula1>"探头订单,备件订单,人工订单,工具订单"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
+      <formula1>"N/A,cancel,badreturn,goodreturn,DOA,shortlife"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
+      <formula1>"N/A,普通,特殊,高值"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{E541982E-D725-4FDA-9EEA-792C8D21CCD5}">
+      <formula1>"N/A,新入保,已入保"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{565EFFCF-906C-4E8B-B682-B8B385A4F816}">
+      <formula1>"East,North,South,West"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{60F15405-71E4-4B57-8AC8-C724A2E36699}">
+      <formula1>"DI,PCB,Biomed,CCS,CCS-A,CCS-B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
+      <formula1>"Depot FE,N/A,TSE,代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:AC1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
-      <formula1>"探头订单,备件订单,人工订单,工具订单"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
-      <formula1>"N/A,cancel,badreturn,goodreturn,DOA,shortlife"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
-      <formula1>"N/A,普通,特殊,高值"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576" xr:uid="{E541982E-D725-4FDA-9EEA-792C8D21CCD5}">
-      <formula1>"N/A,新入保,已入保"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{565EFFCF-906C-4E8B-B682-B8B385A4F816}">
-      <formula1>"East,North,South,West"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{60F15405-71E4-4B57-8AC8-C724A2E36699}">
-      <formula1>"DI,PCB,Biomed,CCS,CCS-A,CCS-B"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
-      <formula1>"Depot FE,N/A,TSE,代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (13)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (14)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD6E08B-8E47-4DF3-9D37-02C564635279}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBD7997-E42E-47D7-9B31-8E7365CDEFA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,17 +507,18 @@
     <col min="7" max="7" width="26.6640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="22.77734375" style="4" customWidth="1"/>
     <col min="9" max="12" width="20.44140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" style="3" customWidth="1"/>
-    <col min="14" max="15" width="20.33203125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="24.33203125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="20.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="23.5546875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="19.88671875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="18.88671875" style="5" customWidth="1"/>
-    <col min="22" max="23" width="17.33203125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="17.88671875" style="2" customWidth="1"/>
-    <col min="25" max="29" width="25.88671875" style="3" customWidth="1"/>
+    <col min="13" max="16" width="25.88671875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="26.6640625" style="3" customWidth="1"/>
+    <col min="18" max="19" width="20.33203125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="24.33203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="20.21875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="23.5546875" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.88671875" style="2" customWidth="1"/>
+    <col min="24" max="24" width="16.77734375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" style="5" customWidth="1"/>
+    <col min="26" max="27" width="17.33203125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="17.88671875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="25.88671875" style="3" customWidth="1"/>
     <col min="30" max="31" width="19.6640625" style="2" customWidth="1"/>
     <col min="32" max="32" width="17.88671875" style="2" customWidth="1"/>
     <col min="33" max="33" width="21.44140625" style="2" customWidth="1"/>
@@ -565,55 +566,55 @@
         <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>17</v>
@@ -660,19 +661,19 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2:AO1048576 AJ2:AJ1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H1048576 N2:N1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H1048576 R2:R1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
       <formula1>1</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:M1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:L1048576 Q2:Q1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
       <formula1>"探头订单,备件订单,人工订单,工具订单"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
@@ -693,7 +694,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
       <formula1>"Depot FE,N/A,TSE,代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:AC1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 M2:P1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>

--- a/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/orderHistory/Order_History_Service_Export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (14)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (5)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBD7997-E42E-47D7-9B31-8E7365CDEFA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62218D3-2BCC-4721-880F-6E163C270D3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>系统ID</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>高值限额</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E5EE65-1D54-4A5B-BDC5-DBB4F002F6AB}">
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5546875" style="2" customWidth="1"/>
@@ -509,26 +512,27 @@
     <col min="9" max="12" width="20.44140625" style="3" customWidth="1"/>
     <col min="13" max="16" width="25.88671875" style="3" customWidth="1"/>
     <col min="17" max="17" width="26.6640625" style="3" customWidth="1"/>
-    <col min="18" max="19" width="20.33203125" style="4" customWidth="1"/>
-    <col min="20" max="20" width="24.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="20.21875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="23.5546875" style="2" customWidth="1"/>
-    <col min="23" max="23" width="19.88671875" style="2" customWidth="1"/>
-    <col min="24" max="24" width="16.77734375" style="2" customWidth="1"/>
-    <col min="25" max="25" width="18.88671875" style="5" customWidth="1"/>
-    <col min="26" max="27" width="17.33203125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="17.88671875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="25.88671875" style="3" customWidth="1"/>
-    <col min="30" max="31" width="19.6640625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="17.88671875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.44140625" style="2" customWidth="1"/>
-    <col min="34" max="37" width="22.109375" style="2" customWidth="1"/>
-    <col min="38" max="40" width="21.6640625" style="2" customWidth="1"/>
-    <col min="41" max="41" width="24.5546875" style="2" customWidth="1"/>
-    <col min="42" max="16384" width="8.88671875" style="2"/>
+    <col min="18" max="18" width="24.33203125" style="2" customWidth="1"/>
+    <col min="19" max="20" width="20.33203125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="24.33203125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="20.21875" style="2" customWidth="1"/>
+    <col min="23" max="23" width="23.5546875" style="2" customWidth="1"/>
+    <col min="24" max="24" width="19.88671875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="16.77734375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="18.88671875" style="5" customWidth="1"/>
+    <col min="27" max="28" width="17.33203125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="17.88671875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="25.88671875" style="3" customWidth="1"/>
+    <col min="31" max="32" width="19.6640625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="17.88671875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.44140625" style="2" customWidth="1"/>
+    <col min="35" max="38" width="22.109375" style="2" customWidth="1"/>
+    <col min="39" max="41" width="21.6640625" style="2" customWidth="1"/>
+    <col min="42" max="42" width="24.5546875" style="2" customWidth="1"/>
+    <col min="43" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,75 +585,78 @@
         <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -658,31 +665,31 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2328E975-6B95-406D-A1DC-1FE2591DFBCB}">
       <formula1>"DI、PCB,US、Biomed,LCS,US探头"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2:AO1048576 AJ2:AJ1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK1048576 AP2:AP1048576" xr:uid="{A51DFEA4-85BF-4073-84EF-6568AF66F0A5}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H1048576 R2:R1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 G2:H1048576" xr:uid="{BF8FCE24-812C-4E76-8679-0BCA72EC8232}">
       <formula1>1</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:L1048576 Q2:Q1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 I2:L1048576" xr:uid="{ABCE1C6A-DD95-44E2-ADD1-D66EF47B9D56}">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576" xr:uid="{F1A10A8C-0601-4CEA-83CB-2DF02510BAA1}">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576" xr:uid="{CDDC3228-3434-4A33-AC68-845488680DFF}">
       <formula1>"探头订单,备件订单,人工订单,工具订单"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576" xr:uid="{D311B7E8-EBC8-42E3-BDCA-16C6F9AAA5F8}">
       <formula1>"N/A,cancel,badreturn,goodreturn,DOA,shortlife"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ1048576" xr:uid="{55F8E1A3-69FF-42C0-9015-A55922B573DE}">
       <formula1>"N/A,普通,特殊,高值"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576" xr:uid="{E541982E-D725-4FDA-9EEA-792C8D21CCD5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576" xr:uid="{E541982E-D725-4FDA-9EEA-792C8D21CCD5}">
       <formula1>"N/A,新入保,已入保"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{565EFFCF-906C-4E8B-B682-B8B385A4F816}">
@@ -691,10 +698,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{60F15405-71E4-4B57-8AC8-C724A2E36699}">
       <formula1>"DI,PCB,Biomed,CCS,CCS-A,CCS-B"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM1048576" xr:uid="{9115FCB4-EFF8-4143-ACB5-03D47345E254}">
       <formula1>"Depot FE,N/A,TSE,代理商,GE FE,Vendor2.0 FE,MVS FE"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 M2:P1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:P1048576 AD2:AD1048576" xr:uid="{DD333222-F32B-486C-95EA-C7A2B140EC69}">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
